--- a/Специальности/ТИС_Техник_инф_систем/02_Тематический_план/Тематический_план_ИКТ_ТИС.xlsx
+++ b/Специальности/ТИС_Техник_инф_систем/02_Тематический_план/Тематический_план_ИКТ_ТИС.xlsx
@@ -1,30 +1,42 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daniy\Documents\Работа с Claud.Ai\ВСе для ИКТ\Специальности\ТИС_Техник_инф_систем\02_Тематический_план\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{961777A0-C0DF-4D41-8CD2-53FC5C9A13C5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13800" windowHeight="13800" xr2:uid="{5DCC104A-CFD1-4711-B4FB-D24CCE0D96D0}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="ИКТ РПО" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Application>Microsoft Excel</Application>
+  <DocSecurity>0</DocSecurity>
+  <ScaleCrop>false</ScaleCrop>
+  <HeadingPairs>
+    <vt:vector size="2" baseType="variant">
+      <vt:variant>
+        <vt:lpstr>Листы</vt:lpstr>
+      </vt:variant>
+      <vt:variant>
+        <vt:i4>1</vt:i4>
+      </vt:variant>
+    </vt:vector>
+  </HeadingPairs>
+  <TitlesOfParts>
+    <vt:vector size="1" baseType="lpstr">
+      <vt:lpstr>ИКТ РПО</vt:lpstr>
+    </vt:vector>
+  </TitlesOfParts>
+  <Company/>
+  <LinksUpToDate>false</LinksUpToDate>
+  <SharedDoc>false</SharedDoc>
+  <HyperlinksChanged>false</HyperlinksChanged>
+  <AppVersion>16.0300</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dc:creator>Daniyar Kaliaskarov</dc:creator>
+  <cp:lastModifiedBy>Daniyar Kaliaskarov</cp:lastModifiedBy>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-06-20T09:43:51Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-06-20T09:43:54Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="111">
   <si>
     <t>Тематический план модуля «Применение ИКТ и цифровых технологий» — ТИС, Техник информационных систем (4S06130105). 96 ч / 4 кр, 3 семестр, зачёт. СРС 72 ч.</t>
@@ -362,7 +374,7 @@
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -506,7 +518,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
     <a:clrScheme name="Стандартная">
@@ -801,7 +813,32 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daniy\Documents\Работа с Claud.Ai\ВСе для ИКТ\Специальности\ТИС_Техник_инф_систем\02_Тематический_план\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{961777A0-C0DF-4D41-8CD2-53FC5C9A13C5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13800" windowHeight="13800" xr2:uid="{5DCC104A-CFD1-4711-B4FB-D24CCE0D96D0}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="ИКТ ТИС" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E535F13-AD69-41C8-AD6D-8FBE5E4AF903}">
   <dimension ref="A1:L48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -819,8 +856,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Тематический план модуля «Применение ИКТ и цифровых технологий» — ТИС, Техник информационных систем (4S06130105). Форма обучения: 9 кл, 4 года. 96 ч / 4 кр, семестры 3–4, зачёт (РО 2.1 и РО 2.2 — 3 семестр; отдельные часы на зачёт не выделяются, оценка по текущим). СРС 72 ч.</t>
+        </is>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -895,8 +934,10 @@
       <c r="B4" s="5">
         <v>2.1</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>14</v>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Изучить роль ИКТ и цифровых технологий в разработке и сопровождении информационных систем</t>
+        </is>
       </c>
       <c r="D4" s="11">
         <v>2</v>
@@ -904,20 +945,21 @@
       <c r="E4" s="11">
         <v>2</v>
       </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
       <c r="I4" s="11">
         <v>2</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="K4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>17</v>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>Эссе: цифровые технологии в работе техника информационных систем</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>все ПМ</t>
+        </is>
       </c>
     </row>
     <row r="5" spans="1:12" ht="150" x14ac:dyDescent="0.25">
@@ -936,9 +978,6 @@
       <c r="E5" s="11">
         <v>2</v>
       </c>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
       <c r="I5" s="11">
         <v>2</v>
       </c>
@@ -948,8 +987,10 @@
       <c r="K5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="L5" s="7" t="s">
-        <v>20</v>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 1</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="1:12" ht="120" x14ac:dyDescent="0.25">
@@ -965,23 +1006,27 @@
       <c r="D6" s="11">
         <v>2</v>
       </c>
-      <c r="E6" s="11"/>
+      <c r="E6" s="11">
+        <v>1</v>
+      </c>
       <c r="F6" s="11">
-        <v>2</v>
-      </c>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
+        <v>1</v>
+      </c>
       <c r="I6" s="11">
         <v>2</v>
       </c>
-      <c r="J6" s="7" t="s">
-        <v>22</v>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Комбинир.</t>
+        </is>
       </c>
       <c r="K6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="L6" s="7" t="s">
-        <v>17</v>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 1, ПМ 2</t>
+        </is>
       </c>
     </row>
     <row r="7" spans="1:12" ht="180" x14ac:dyDescent="0.25">
@@ -1000,8 +1045,6 @@
       <c r="E7" s="11">
         <v>1</v>
       </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
       <c r="H7" s="11">
         <v>1</v>
       </c>
@@ -1014,8 +1057,10 @@
       <c r="K7" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="L7" s="7" t="s">
-        <v>27</v>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 3, ПМ 4</t>
+        </is>
       </c>
     </row>
     <row r="8" spans="1:12" ht="150" x14ac:dyDescent="0.25">
@@ -1031,11 +1076,9 @@
       <c r="D8" s="11">
         <v>2</v>
       </c>
-      <c r="E8" s="11"/>
       <c r="F8" s="11">
         <v>1</v>
       </c>
-      <c r="G8" s="11"/>
       <c r="H8" s="11">
         <v>1</v>
       </c>
@@ -1048,8 +1091,10 @@
       <c r="K8" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="L8" s="7" t="s">
-        <v>30</v>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 1, ПМ 7</t>
+        </is>
       </c>
     </row>
     <row r="9" spans="1:12" ht="135" x14ac:dyDescent="0.25">
@@ -1065,11 +1110,9 @@
       <c r="D9" s="11">
         <v>2</v>
       </c>
-      <c r="E9" s="11"/>
       <c r="F9" s="11">
         <v>1</v>
       </c>
-      <c r="G9" s="11"/>
       <c r="H9" s="11">
         <v>1</v>
       </c>
@@ -1082,8 +1125,10 @@
       <c r="K9" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L9" s="7" t="s">
-        <v>33</v>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 5, ПМ 7</t>
+        </is>
       </c>
     </row>
     <row r="10" spans="1:12" ht="105" x14ac:dyDescent="0.25">
@@ -1099,11 +1144,9 @@
       <c r="D10" s="11">
         <v>2</v>
       </c>
-      <c r="E10" s="11"/>
       <c r="F10" s="11">
         <v>1</v>
       </c>
-      <c r="G10" s="11"/>
       <c r="H10" s="11">
         <v>1</v>
       </c>
@@ -1116,8 +1159,10 @@
       <c r="K10" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="L10" s="7" t="s">
-        <v>30</v>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 7</t>
+        </is>
       </c>
     </row>
     <row r="11" spans="1:12" ht="120" x14ac:dyDescent="0.25">
@@ -1139,8 +1184,6 @@
       <c r="F11" s="11">
         <v>1</v>
       </c>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
       <c r="I11" s="11">
         <v>2</v>
       </c>
@@ -1150,7 +1193,11 @@
       <c r="K11" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="L11" s="7"/>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 2, ПМ 6</t>
+        </is>
+      </c>
     </row>
     <row r="12" spans="1:12" ht="165" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
@@ -1165,11 +1212,9 @@
       <c r="D12" s="11">
         <v>2</v>
       </c>
-      <c r="E12" s="11"/>
       <c r="F12" s="11">
         <v>1</v>
       </c>
-      <c r="G12" s="11"/>
       <c r="H12" s="11">
         <v>1</v>
       </c>
@@ -1182,7 +1227,11 @@
       <c r="K12" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="L12" s="7"/>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 2, ПМ 6</t>
+        </is>
+      </c>
     </row>
     <row r="13" spans="1:12" ht="135" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
@@ -1200,9 +1249,6 @@
       <c r="E13" s="11">
         <v>2</v>
       </c>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
       <c r="I13" s="11">
         <v>2</v>
       </c>
@@ -1212,7 +1258,11 @@
       <c r="K13" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L13" s="7"/>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 5, ПМ 7</t>
+        </is>
+      </c>
     </row>
     <row r="14" spans="1:12" ht="165" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
@@ -1227,11 +1277,9 @@
       <c r="D14" s="11">
         <v>2</v>
       </c>
-      <c r="E14" s="11"/>
       <c r="F14" s="11">
         <v>1</v>
       </c>
-      <c r="G14" s="11"/>
       <c r="H14" s="11">
         <v>1</v>
       </c>
@@ -1244,8 +1292,10 @@
       <c r="K14" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L14" s="7" t="s">
-        <v>17</v>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>все ПМ</t>
+        </is>
       </c>
     </row>
     <row r="15" spans="1:12" ht="135" x14ac:dyDescent="0.25">
@@ -1261,23 +1311,27 @@
       <c r="D15" s="11">
         <v>2</v>
       </c>
-      <c r="E15" s="11"/>
+      <c r="E15" s="11">
+        <v>1</v>
+      </c>
       <c r="F15" s="11">
-        <v>2</v>
-      </c>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
+        <v>1</v>
+      </c>
       <c r="I15" s="11">
         <v>2</v>
       </c>
-      <c r="J15" s="7" t="s">
-        <v>22</v>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Комбинир.</t>
+        </is>
       </c>
       <c r="K15" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L15" s="7" t="s">
-        <v>17</v>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 6</t>
+        </is>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -1312,9 +1366,6 @@
       <c r="E17" s="11">
         <v>2</v>
       </c>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
       <c r="I17" s="11">
         <v>2</v>
       </c>
@@ -1324,7 +1375,11 @@
       <c r="K17" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="L17" s="7"/>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 7</t>
+        </is>
+      </c>
     </row>
     <row r="18" spans="1:12" ht="120" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
@@ -1339,11 +1394,9 @@
       <c r="D18" s="11">
         <v>2</v>
       </c>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11">
-        <v>1</v>
-      </c>
-      <c r="G18" s="11"/>
+      <c r="E18" s="11">
+        <v>1</v>
+      </c>
       <c r="H18" s="11">
         <v>1</v>
       </c>
@@ -1356,7 +1409,11 @@
       <c r="K18" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="L18" s="7"/>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 7</t>
+        </is>
+      </c>
     </row>
     <row r="19" spans="1:12" ht="150" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
@@ -1371,22 +1428,28 @@
       <c r="D19" s="11">
         <v>2</v>
       </c>
-      <c r="E19" s="11"/>
+      <c r="E19" s="11">
+        <v>1</v>
+      </c>
       <c r="F19" s="11">
-        <v>2</v>
-      </c>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
+        <v>1</v>
+      </c>
       <c r="I19" s="11">
         <v>2</v>
       </c>
-      <c r="J19" s="7" t="s">
-        <v>22</v>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Комбинир.</t>
+        </is>
       </c>
       <c r="K19" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="L19" s="7"/>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 7</t>
+        </is>
+      </c>
     </row>
     <row r="20" spans="1:12" ht="150" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
@@ -1401,23 +1464,27 @@
       <c r="D20" s="11">
         <v>2</v>
       </c>
-      <c r="E20" s="11"/>
+      <c r="E20" s="11">
+        <v>1</v>
+      </c>
       <c r="F20" s="11">
-        <v>2</v>
-      </c>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
+        <v>1</v>
+      </c>
       <c r="I20" s="11">
         <v>2</v>
       </c>
-      <c r="J20" s="7" t="s">
-        <v>22</v>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>Комбинир.</t>
+        </is>
       </c>
       <c r="K20" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="L20" s="7" t="s">
-        <v>17</v>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>все ПМ</t>
+        </is>
       </c>
     </row>
     <row r="21" spans="1:12" ht="150" x14ac:dyDescent="0.25">
@@ -1433,22 +1500,28 @@
       <c r="D21" s="11">
         <v>2</v>
       </c>
-      <c r="E21" s="11"/>
+      <c r="E21" s="11">
+        <v>1</v>
+      </c>
       <c r="F21" s="11">
-        <v>2</v>
-      </c>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
+        <v>1</v>
+      </c>
       <c r="I21" s="11">
         <v>2</v>
       </c>
-      <c r="J21" s="7" t="s">
-        <v>22</v>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>Комбинир.</t>
+        </is>
       </c>
       <c r="K21" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L21" s="7"/>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 7</t>
+        </is>
+      </c>
     </row>
     <row r="22" spans="1:12" ht="135" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
@@ -1463,11 +1536,9 @@
       <c r="D22" s="11">
         <v>2</v>
       </c>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11">
-        <v>1</v>
-      </c>
-      <c r="G22" s="11"/>
+      <c r="E22" s="11">
+        <v>1</v>
+      </c>
       <c r="H22" s="11">
         <v>1</v>
       </c>
@@ -1480,7 +1551,11 @@
       <c r="K22" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L22" s="7"/>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 7</t>
+        </is>
+      </c>
     </row>
     <row r="23" spans="1:12" ht="135" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
@@ -1495,23 +1570,27 @@
       <c r="D23" s="11">
         <v>2</v>
       </c>
-      <c r="E23" s="11"/>
+      <c r="E23" s="11">
+        <v>1</v>
+      </c>
       <c r="F23" s="11">
-        <v>2</v>
-      </c>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
+        <v>1</v>
+      </c>
       <c r="I23" s="11">
         <v>2</v>
       </c>
-      <c r="J23" s="7" t="s">
-        <v>22</v>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>Комбинир.</t>
+        </is>
       </c>
       <c r="K23" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L23" s="7" t="s">
-        <v>61</v>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 5, ПМ 7</t>
+        </is>
       </c>
     </row>
     <row r="24" spans="1:12" ht="195" x14ac:dyDescent="0.25">
@@ -1533,8 +1612,6 @@
       <c r="F24" s="11">
         <v>1</v>
       </c>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
       <c r="I24" s="11">
         <v>2</v>
       </c>
@@ -1544,8 +1621,10 @@
       <c r="K24" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="L24" s="7" t="s">
-        <v>17</v>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 1, ПМ 3</t>
+        </is>
       </c>
     </row>
     <row r="25" spans="1:12" ht="165" x14ac:dyDescent="0.25">
@@ -1561,11 +1640,9 @@
       <c r="D25" s="11">
         <v>2</v>
       </c>
-      <c r="E25" s="11"/>
       <c r="F25" s="11">
         <v>1</v>
       </c>
-      <c r="G25" s="11"/>
       <c r="H25" s="11">
         <v>1</v>
       </c>
@@ -1578,7 +1655,11 @@
       <c r="K25" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="L25" s="7"/>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>все ПМ</t>
+        </is>
+      </c>
     </row>
     <row r="26" spans="1:12" ht="150" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
@@ -1593,11 +1674,9 @@
       <c r="D26" s="11">
         <v>2</v>
       </c>
-      <c r="E26" s="11"/>
       <c r="F26" s="11">
         <v>1</v>
       </c>
-      <c r="G26" s="11"/>
       <c r="H26" s="11">
         <v>1</v>
       </c>
@@ -1610,7 +1689,11 @@
       <c r="K26" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="L26" s="7"/>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>все ПМ</t>
+        </is>
+      </c>
     </row>
     <row r="27" spans="1:12" ht="165" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
@@ -1625,22 +1708,28 @@
       <c r="D27" s="11">
         <v>2</v>
       </c>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11">
-        <v>2</v>
-      </c>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
+      <c r="E27" s="11">
+        <v>1</v>
+      </c>
+      <c r="H27" s="11">
+        <v>1</v>
+      </c>
       <c r="I27" s="11">
         <v>2</v>
       </c>
-      <c r="J27" s="7" t="s">
-        <v>22</v>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>Комбинир.</t>
+        </is>
       </c>
       <c r="K27" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="L27" s="7"/>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 7</t>
+        </is>
+      </c>
     </row>
     <row r="28" spans="1:12" ht="165" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
@@ -1655,11 +1744,9 @@
       <c r="D28" s="11">
         <v>2</v>
       </c>
-      <c r="E28" s="11"/>
       <c r="F28" s="11">
         <v>1</v>
       </c>
-      <c r="G28" s="11"/>
       <c r="H28" s="11">
         <v>1</v>
       </c>
@@ -1672,7 +1759,11 @@
       <c r="K28" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="L28" s="7"/>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 7</t>
+        </is>
+      </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
@@ -1706,9 +1797,6 @@
       <c r="E30" s="11">
         <v>2</v>
       </c>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
       <c r="I30" s="11">
         <v>2</v>
       </c>
@@ -1718,8 +1806,10 @@
       <c r="K30" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="L30" s="7" t="s">
-        <v>75</v>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>все ПМ</t>
+        </is>
       </c>
     </row>
     <row r="31" spans="1:12" ht="210" x14ac:dyDescent="0.25">
@@ -1735,25 +1825,30 @@
       <c r="D31" s="11">
         <v>6</v>
       </c>
-      <c r="E31" s="11"/>
+      <c r="E31" s="11">
+        <v>2</v>
+      </c>
       <c r="F31" s="11">
-        <v>5</v>
-      </c>
-      <c r="G31" s="11"/>
+        <v>3</v>
+      </c>
       <c r="H31" s="11">
         <v>1</v>
       </c>
       <c r="I31" s="11">
         <v>2</v>
       </c>
-      <c r="J31" s="7" t="s">
-        <v>22</v>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>Комбинир.</t>
+        </is>
       </c>
       <c r="K31" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="L31" s="7" t="s">
-        <v>78</v>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 3, ПМ 4</t>
+        </is>
       </c>
     </row>
     <row r="32" spans="1:12" ht="135" x14ac:dyDescent="0.25">
@@ -1769,25 +1864,30 @@
       <c r="D32" s="11">
         <v>4</v>
       </c>
-      <c r="E32" s="11"/>
+      <c r="E32" s="11">
+        <v>2</v>
+      </c>
       <c r="F32" s="11">
-        <v>3</v>
-      </c>
-      <c r="G32" s="11"/>
+        <v>1</v>
+      </c>
       <c r="H32" s="11">
         <v>1</v>
       </c>
       <c r="I32" s="11">
         <v>2</v>
       </c>
-      <c r="J32" s="7" t="s">
-        <v>22</v>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>Комбинир.</t>
+        </is>
       </c>
       <c r="K32" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="L32" s="7" t="s">
-        <v>27</v>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 3, ПМ 4</t>
+        </is>
       </c>
     </row>
     <row r="33" spans="1:12" ht="135" x14ac:dyDescent="0.25">
@@ -1803,25 +1903,30 @@
       <c r="D33" s="11">
         <v>4</v>
       </c>
-      <c r="E33" s="11"/>
+      <c r="E33" s="11">
+        <v>2</v>
+      </c>
       <c r="F33" s="11">
-        <v>3</v>
-      </c>
-      <c r="G33" s="11"/>
+        <v>1</v>
+      </c>
       <c r="H33" s="11">
         <v>1</v>
       </c>
       <c r="I33" s="11">
         <v>2</v>
       </c>
-      <c r="J33" s="7" t="s">
-        <v>22</v>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>Комбинир.</t>
+        </is>
       </c>
       <c r="K33" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="L33" s="7" t="s">
-        <v>83</v>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 3, ПМ 4</t>
+        </is>
       </c>
     </row>
     <row r="34" spans="1:12" ht="120" x14ac:dyDescent="0.25">
@@ -1838,26 +1943,29 @@
         <v>6</v>
       </c>
       <c r="E34" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="11">
-        <v>4</v>
-      </c>
-      <c r="G34" s="11"/>
+        <v>3</v>
+      </c>
       <c r="H34" s="11">
         <v>1</v>
       </c>
       <c r="I34" s="11">
         <v>2</v>
       </c>
-      <c r="J34" s="7" t="s">
-        <v>22</v>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>Комбинир.</t>
+        </is>
       </c>
       <c r="K34" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="L34" s="7" t="s">
-        <v>86</v>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 3, ПМ 5</t>
+        </is>
       </c>
     </row>
     <row r="35" spans="1:12" ht="165" x14ac:dyDescent="0.25">
@@ -1873,23 +1981,27 @@
       <c r="D35" s="11">
         <v>4</v>
       </c>
-      <c r="E35" s="11"/>
+      <c r="E35" s="11">
+        <v>2</v>
+      </c>
       <c r="F35" s="11">
-        <v>4</v>
-      </c>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
+        <v>2</v>
+      </c>
       <c r="I35" s="11">
         <v>2</v>
       </c>
-      <c r="J35" s="7" t="s">
-        <v>22</v>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>Комбинир.</t>
+        </is>
       </c>
       <c r="K35" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="L35" s="7" t="s">
-        <v>61</v>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 5</t>
+        </is>
       </c>
     </row>
     <row r="36" spans="1:12" ht="90" x14ac:dyDescent="0.25">
@@ -1905,23 +2017,27 @@
       <c r="D36" s="11">
         <v>2</v>
       </c>
-      <c r="E36" s="11"/>
+      <c r="E36" s="11">
+        <v>1</v>
+      </c>
       <c r="F36" s="11">
-        <v>2</v>
-      </c>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
+        <v>1</v>
+      </c>
       <c r="I36" s="11">
         <v>2</v>
       </c>
-      <c r="J36" s="7" t="s">
-        <v>22</v>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>Комбинир.</t>
+        </is>
       </c>
       <c r="K36" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="L36" s="7" t="s">
-        <v>33</v>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 5, ПМ 7</t>
+        </is>
       </c>
     </row>
     <row r="37" spans="1:12" ht="120" x14ac:dyDescent="0.25">
@@ -1937,12 +2053,10 @@
       <c r="D37" s="11">
         <v>2</v>
       </c>
-      <c r="E37" s="11"/>
+      <c r="E37" s="11">
+        <v>1</v>
+      </c>
       <c r="F37" s="11">
-        <v>1</v>
-      </c>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11">
         <v>1</v>
       </c>
       <c r="I37" s="11">
@@ -1954,8 +2068,10 @@
       <c r="K37" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="L37" s="7" t="s">
-        <v>33</v>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 5</t>
+        </is>
       </c>
     </row>
     <row r="38" spans="1:12" ht="150" x14ac:dyDescent="0.25">
@@ -1971,23 +2087,27 @@
       <c r="D38" s="11">
         <v>2</v>
       </c>
-      <c r="E38" s="11"/>
+      <c r="E38" s="11">
+        <v>1</v>
+      </c>
       <c r="F38" s="11">
-        <v>2</v>
-      </c>
-      <c r="G38" s="11"/>
-      <c r="H38" s="11"/>
+        <v>1</v>
+      </c>
       <c r="I38" s="11">
         <v>2</v>
       </c>
       <c r="J38" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="K38" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L38" s="7" t="s">
-        <v>95</v>
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>Сценарий применения ИИ-агента в задаче сопровождения информационной системы</t>
+        </is>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 6, ПМ 7</t>
+        </is>
       </c>
     </row>
     <row r="39" spans="1:12" ht="105" x14ac:dyDescent="0.25">
@@ -2004,12 +2124,11 @@
         <v>4</v>
       </c>
       <c r="E39" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="11">
-        <v>2</v>
-      </c>
-      <c r="G39" s="11"/>
+        <v>1</v>
+      </c>
       <c r="H39" s="11">
         <v>1</v>
       </c>
@@ -2022,8 +2141,10 @@
       <c r="K39" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="L39" s="7" t="s">
-        <v>95</v>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 6, ПМ 7</t>
+        </is>
       </c>
     </row>
     <row r="40" spans="1:12" ht="165" x14ac:dyDescent="0.25">
@@ -2039,25 +2160,30 @@
       <c r="D40" s="11">
         <v>4</v>
       </c>
-      <c r="E40" s="11"/>
+      <c r="E40" s="11">
+        <v>1</v>
+      </c>
       <c r="F40" s="11">
-        <v>3</v>
-      </c>
-      <c r="G40" s="11"/>
+        <v>2</v>
+      </c>
       <c r="H40" s="11">
         <v>1</v>
       </c>
       <c r="I40" s="11">
         <v>2</v>
       </c>
-      <c r="J40" s="7" t="s">
-        <v>22</v>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>Комбинир.</t>
+        </is>
       </c>
       <c r="K40" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="L40" s="7" t="s">
-        <v>95</v>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 7</t>
+        </is>
       </c>
     </row>
     <row r="41" spans="1:12" ht="210" x14ac:dyDescent="0.25">
@@ -2076,9 +2202,6 @@
       <c r="E41" s="11">
         <v>2</v>
       </c>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
       <c r="I41" s="11">
         <v>2</v>
       </c>
@@ -2088,7 +2211,11 @@
       <c r="K41" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="L41" s="7"/>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>все ПМ</t>
+        </is>
+      </c>
     </row>
     <row r="42" spans="1:12" ht="135" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
@@ -2106,15 +2233,16 @@
       <c r="E42" s="11">
         <v>2</v>
       </c>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11"/>
       <c r="I42" s="11"/>
       <c r="J42" s="7" t="s">
         <v>15</v>
       </c>
       <c r="K42" s="7"/>
-      <c r="L42" s="7"/>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>все ПМ</t>
+        </is>
+      </c>
     </row>
     <row r="43" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
@@ -2129,19 +2257,18 @@
       <c r="D43" s="11">
         <v>2</v>
       </c>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11">
-        <v>2</v>
-      </c>
-      <c r="H43" s="11"/>
+      <c r="F43" s="11">
+        <v>2</v>
+      </c>
       <c r="I43" s="11"/>
       <c r="J43" s="7" t="s">
         <v>105</v>
       </c>
       <c r="K43" s="7"/>
-      <c r="L43" s="7" t="s">
-        <v>30</v>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>ПМ 3, ПМ 7</t>
+        </is>
       </c>
     </row>
     <row r="44" spans="1:12" ht="135" x14ac:dyDescent="0.25">
@@ -2157,19 +2284,18 @@
       <c r="D44" s="11">
         <v>2</v>
       </c>
-      <c r="E44" s="11"/>
       <c r="F44" s="11">
         <v>2</v>
       </c>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
       <c r="I44" s="11"/>
       <c r="J44" s="7" t="s">
         <v>107</v>
       </c>
       <c r="K44" s="7"/>
-      <c r="L44" s="7" t="s">
-        <v>30</v>
+      <c r="L44" s="7" t="inlineStr">
+        <is>
+          <t>все ПМ</t>
+        </is>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -2182,13 +2308,10 @@
         <v>96</v>
       </c>
       <c r="E45" s="12">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F45" s="12">
-        <v>57</v>
-      </c>
-      <c r="G45" s="12">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="H45" s="12">
         <v>18</v>
